--- a/Result/checksun_type/顯示卡.xlsx
+++ b/Result/checksun_type/顯示卡.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI111"/>
+  <dimension ref="A1:CI121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43542,17 +43542,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6416.499</t>
+          <t>4653.324</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -43562,7 +43562,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>270.5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -43572,17 +43572,17 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-5.66</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>-17.46</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -43592,37 +43592,37 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2025-10-27 00:00:00</t>
+          <t>2025-10-02 00:00:00</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2025-11-03 00:00:00</t>
+          <t>2025-10-14 00:00:00</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>2025-08-11 00:00:00</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2025-09-30 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>714.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -43632,12 +43632,12 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>289.5</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -43647,27 +43647,27 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
@@ -43678,131 +43678,131 @@
       <c r="AC101" t="inlineStr"/>
       <c r="AD101" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.43</t>
         </is>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>28.72</t>
         </is>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
+          <t>-1.2</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
           <t>0.11</t>
         </is>
       </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>636.8</t>
+          <t>272.5</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>678.2</t>
+          <t>277.7</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>677.46</t>
+          <t>281.06</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>665.81</t>
+          <t>280.76</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>-175.57</t>
+          <t>-24.95</t>
         </is>
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>-14.12</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="AR101" t="inlineStr">
         <is>
-          <t>-5.12</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr">
         <is>
-          <t>-122.08</t>
+          <t>-111.69</t>
         </is>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/09/09</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>5203739969.20767</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>3971577357.0</t>
+          <t>1251572407.0</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>3110892215.0</t>
+          <t>896460694.0</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>2577610128.3</t>
+          <t>1086040261.5</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>2089597881.18</t>
+          <t>1638145283.6</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>533282086</t>
+          <t>-189579567</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>112478878.5941267</t>
+          <t>-132899370.9478257</t>
         </is>
       </c>
       <c r="BC101" t="n">
-        <v>272741488.12</v>
+        <v>-106805914.93</v>
       </c>
       <c r="BD101" t="inlineStr">
         <is>
@@ -43811,27 +43811,27 @@
       </c>
       <c r="BE101" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="BF101" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/10/02</t>
         </is>
       </c>
       <c r="BG101" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BI101" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BJ101" t="inlineStr">
@@ -43846,62 +43846,62 @@
       </c>
       <c r="BL101" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM101" t="inlineStr">
         <is>
-          <t>-19.69180399575732</t>
+          <t>1.179095346377122</t>
         </is>
       </c>
       <c r="BN101" t="inlineStr">
         <is>
-          <t>32.8429209193585</t>
+          <t>9.881236321227592</t>
         </is>
       </c>
       <c r="BO101" t="inlineStr">
         <is>
-          <t>24.67740643280432</t>
+          <t>22.46336360303147</t>
         </is>
       </c>
       <c r="BP101" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ101" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR101" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BS101" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT101" t="inlineStr">
         <is>
-          <t>269.64</t>
+          <t>118.80</t>
         </is>
       </c>
       <c r="BU101" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="BV101" t="inlineStr">
         <is>
-          <t>14.33%</t>
+          <t>9.91%</t>
         </is>
       </c>
       <c r="BW101" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="BX101" t="inlineStr">
@@ -43911,52 +43911,52 @@
       </c>
       <c r="BY101" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>171491</t>
         </is>
       </c>
       <c r="BZ101" t="inlineStr">
         <is>
-          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+          <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
         </is>
       </c>
       <c r="CA101" t="inlineStr">
         <is>
-          <t>華碩-電腦及週邊設備業-上市</t>
+          <t>技嘉-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CB101" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CC101" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>266.0</t>
         </is>
       </c>
       <c r="CD101" t="inlineStr">
         <is>
-          <t>637.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="CE101" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>264.0</t>
         </is>
       </c>
       <c r="CF101" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>270.5</t>
         </is>
       </c>
       <c r="CG101" t="inlineStr">
         <is>
-          <t>346.61</t>
+          <t>82.81</t>
         </is>
       </c>
       <c r="CH101" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+          <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
       <c r="CI101" t="inlineStr">
@@ -43973,17 +43973,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>3558.4</t>
+          <t>2102.37</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -43993,7 +43993,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -44003,17 +44003,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>-22.21</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -44023,37 +44023,37 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2025-10-27 00:00:00</t>
+          <t>2025-10-02 00:00:00</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2025-11-03 00:00:00</t>
+          <t>2025-10-14 00:00:00</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>2025-08-11 00:00:00</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2025-09-30 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>714.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -44063,12 +44063,12 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>289.5</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -44078,27 +44078,27 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-3.57</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>11.17</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
@@ -44109,72 +44109,72 @@
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>647.4</t>
+          <t>272.6</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>681.95</t>
+          <t>278.32</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>677.64</t>
+          <t>280.98</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>665.98</t>
+          <t>281.01</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>-270.92</t>
+          <t>-30.35</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
@@ -44184,56 +44184,56 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>-112.39</t>
+          <t>-110.96</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/09/09</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>5203739969.20767</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>2253776059.0</t>
+          <t>569966958.0</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>2660675287.2</t>
+          <t>827665404.2</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>2395309044.8</t>
+          <t>1063949427.6</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>2031062259.28</t>
+          <t>1639177449.86</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>265366242</t>
+          <t>-236284023</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>83340222.31716728</t>
+          <t>-137643635.6775677</t>
         </is>
       </c>
       <c r="BC102" t="n">
-        <v>184622942.89</v>
+        <v>-146254448.27</v>
       </c>
       <c r="BD102" t="inlineStr">
         <is>
@@ -44242,27 +44242,27 @@
       </c>
       <c r="BE102" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/10/02</t>
         </is>
       </c>
       <c r="BG102" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-9.70</t>
         </is>
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BI102" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BJ102" t="inlineStr">
@@ -44277,27 +44277,27 @@
       </c>
       <c r="BL102" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM102" t="inlineStr">
         <is>
-          <t>-19.69180399575732</t>
+          <t>1.179095346377122</t>
         </is>
       </c>
       <c r="BN102" t="inlineStr">
         <is>
-          <t>32.8429209193585</t>
+          <t>9.881236321227592</t>
         </is>
       </c>
       <c r="BO102" t="inlineStr">
         <is>
-          <t>24.67740643280432</t>
+          <t>22.46336360303147</t>
         </is>
       </c>
       <c r="BP102" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ102" t="inlineStr">
@@ -44307,32 +44307,32 @@
       </c>
       <c r="BR102" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BS102" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT102" t="inlineStr">
         <is>
-          <t>269.64</t>
+          <t>118.80</t>
         </is>
       </c>
       <c r="BU102" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="BV102" t="inlineStr">
         <is>
-          <t>14.33%</t>
+          <t>9.91%</t>
         </is>
       </c>
       <c r="BW102" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="BX102" t="inlineStr">
@@ -44342,52 +44342,52 @@
       </c>
       <c r="BY102" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>171491</t>
         </is>
       </c>
       <c r="BZ102" t="inlineStr">
         <is>
-          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+          <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
         </is>
       </c>
       <c r="CA102" t="inlineStr">
         <is>
-          <t>華碩-電腦及週邊設備業-上市</t>
+          <t>技嘉-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CB102" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CC102" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="CD102" t="inlineStr">
         <is>
-          <t>638.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="CE102" t="inlineStr">
         <is>
-          <t>625.0</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="CF102" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="CG102" t="inlineStr">
         <is>
-          <t>346.61</t>
+          <t>82.81</t>
         </is>
       </c>
       <c r="CH102" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+          <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
       <c r="CI102" t="inlineStr">
@@ -44404,17 +44404,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5110.97</t>
+          <t>3450.872</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -44424,7 +44424,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -44434,17 +44434,17 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>14.24</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -44454,37 +44454,37 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2025-10-27 00:00:00</t>
+          <t>2025-10-02 00:00:00</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2025-11-03 00:00:00</t>
+          <t>2025-10-14 00:00:00</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>2025-08-11 00:00:00</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2025-09-30 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>714.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -44494,12 +44494,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>289.5</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -44509,27 +44509,27 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>18.34</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
@@ -44540,131 +44540,131 @@
       <c r="AC103" t="inlineStr"/>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>45.41</t>
         </is>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>653.6</t>
+          <t>274.3</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>684.55</t>
+          <t>278.77</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>677.36</t>
+          <t>281.12</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>666.06</t>
+          <t>281.25</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>-809.67</t>
+          <t>-33.04</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>-8.44</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-2.65</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>-104.00</t>
+          <t>-110.13</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/09/09</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>5203739969.20767</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>3252501668.0</t>
+          <t>936287073.0</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>2688233856.6</t>
+          <t>1113667938.4</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>2353124375.3</t>
+          <t>1099219795.8</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>2012331643.46</t>
+          <t>1643378817.02</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>335109481</t>
+          <t>14448142</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>64925182.21223693</t>
+          <t>-136078033.3887317</t>
         </is>
       </c>
       <c r="BC103" t="n">
-        <v>236195769.4</v>
+        <v>-124356967.48</v>
       </c>
       <c r="BD103" t="inlineStr">
         <is>
@@ -44673,27 +44673,27 @@
       </c>
       <c r="BE103" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/10/02</t>
         </is>
       </c>
       <c r="BG103" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BI103" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BJ103" t="inlineStr">
@@ -44708,62 +44708,62 @@
       </c>
       <c r="BL103" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM103" t="inlineStr">
         <is>
-          <t>-19.69180399575732</t>
+          <t>1.179095346377122</t>
         </is>
       </c>
       <c r="BN103" t="inlineStr">
         <is>
-          <t>32.8429209193585</t>
+          <t>9.881236321227592</t>
         </is>
       </c>
       <c r="BO103" t="inlineStr">
         <is>
-          <t>24.67740643280432</t>
+          <t>22.46336360303147</t>
         </is>
       </c>
       <c r="BP103" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ103" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR103" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BS103" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT103" t="inlineStr">
         <is>
-          <t>269.64</t>
+          <t>118.80</t>
         </is>
       </c>
       <c r="BU103" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="BV103" t="inlineStr">
         <is>
-          <t>14.33%</t>
+          <t>9.91%</t>
         </is>
       </c>
       <c r="BW103" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="BX103" t="inlineStr">
@@ -44773,52 +44773,52 @@
       </c>
       <c r="BY103" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>171491</t>
         </is>
       </c>
       <c r="BZ103" t="inlineStr">
         <is>
-          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+          <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
         </is>
       </c>
       <c r="CA103" t="inlineStr">
         <is>
-          <t>華碩-電腦及週邊設備業-上市</t>
+          <t>技嘉-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CB103" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CC103" t="inlineStr">
         <is>
-          <t>648.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="CD103" t="inlineStr">
         <is>
-          <t>649.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="CE103" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>269.5</t>
         </is>
       </c>
       <c r="CF103" t="inlineStr">
         <is>
-          <t>633.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="CG103" t="inlineStr">
         <is>
-          <t>346.61</t>
+          <t>82.81</t>
         </is>
       </c>
       <c r="CH103" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+          <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
       <c r="CI103" t="inlineStr">
@@ -44835,17 +44835,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6078.152</t>
+          <t>2461.621</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -44855,7 +44855,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -44865,17 +44865,17 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-7.42</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -44885,37 +44885,37 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2025-10-27 00:00:00</t>
+          <t>2025-10-02 00:00:00</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2025-11-03 00:00:00</t>
+          <t>2025-10-14 00:00:00</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>2025-08-11 00:00:00</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2025-09-30 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>714.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -44925,12 +44925,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>289.5</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -44940,27 +44940,27 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
@@ -44971,131 +44971,131 @@
       <c r="AC104" t="inlineStr"/>
       <c r="AD104" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>55.17</t>
         </is>
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>42.37</t>
         </is>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>-3.48</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>663.2</t>
+          <t>273.5</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>687.1</t>
+          <t>279.23</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>677.34</t>
+          <t>281.32</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>666.14</t>
+          <t>281.45</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>-676.47</t>
+          <t>-35.97</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>-95.91</t>
+          <t>-109.29</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/09/09</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>5203739969.20767</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>3950855603.0</t>
+          <t>681575776.0</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>2444767042.2</t>
+          <t>1107816188.0</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>2195634921.6</t>
+          <t>1115793213.5</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>1973519631.2</t>
+          <t>1639284497.76</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>249132120</t>
+          <t>-7977025</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>33785075.45068976</t>
+          <t>-138209136.2810771</t>
         </is>
       </c>
       <c r="BC104" t="n">
-        <v>194429357.4</v>
+        <v>-127882115.56</v>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
@@ -45104,27 +45104,27 @@
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/10/02</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr">
@@ -45139,62 +45139,62 @@
       </c>
       <c r="BL104" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM104" t="inlineStr">
         <is>
-          <t>-19.69180399575732</t>
+          <t>1.179095346377122</t>
         </is>
       </c>
       <c r="BN104" t="inlineStr">
         <is>
-          <t>32.8429209193585</t>
+          <t>9.881236321227592</t>
         </is>
       </c>
       <c r="BO104" t="inlineStr">
         <is>
-          <t>24.67740643280432</t>
+          <t>22.46336360303147</t>
         </is>
       </c>
       <c r="BP104" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ104" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR104" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="BS104" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT104" t="inlineStr">
         <is>
-          <t>269.64</t>
+          <t>118.80</t>
         </is>
       </c>
       <c r="BU104" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="BV104" t="inlineStr">
         <is>
-          <t>14.33%</t>
+          <t>9.91%</t>
         </is>
       </c>
       <c r="BW104" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="BX104" t="inlineStr">
@@ -45204,52 +45204,52 @@
       </c>
       <c r="BY104" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>171491</t>
         </is>
       </c>
       <c r="BZ104" t="inlineStr">
         <is>
-          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+          <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
         </is>
       </c>
       <c r="CA104" t="inlineStr">
         <is>
-          <t>華碩-電腦及週邊設備業-上市</t>
+          <t>技嘉-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CB104" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CC104" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>277.5</t>
         </is>
       </c>
       <c r="CD104" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="CE104" t="inlineStr">
         <is>
-          <t>646.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="CF104" t="inlineStr">
         <is>
-          <t>647.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="CG104" t="inlineStr">
         <is>
-          <t>346.61</t>
+          <t>82.81</t>
         </is>
       </c>
       <c r="CH104" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+          <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
       <c r="CI104" t="inlineStr">
@@ -45266,17 +45266,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>3200.569</t>
+          <t>3815.004</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -45286,7 +45286,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -45296,17 +45296,17 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-8.36</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>11.48</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -45316,37 +45316,37 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2025-10-27 00:00:00</t>
+          <t>2025-10-02 00:00:00</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2025-11-03 00:00:00</t>
+          <t>2025-10-14 00:00:00</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>2025-08-11 00:00:00</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2025-09-30 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>714.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -45356,12 +45356,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>289.5</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -45371,27 +45371,27 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14.79</t>
+          <t>20.27</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
@@ -45402,131 +45402,131 @@
       <c r="AC105" t="inlineStr"/>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>43.64</t>
         </is>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>271.9</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>689.1</t>
+          <t>279.92</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>677.08</t>
+          <t>281.51</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>666.05</t>
+          <t>281.57</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>-219.00</t>
+          <t>-52.95</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-108.46</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/09/09</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>5203739969.20767</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>2125750388.0</t>
+          <t>1042901256.0</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>2117069946.2</t>
+          <t>1308033612.8</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>1936357091.0</t>
+          <t>1173335676.5</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>1916414460.46</t>
+          <t>1644815841.24</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>180712855</t>
+          <t>134697936</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>4577024.187966792</t>
+          <t>-140086776.412902</t>
         </is>
       </c>
       <c r="BC105" t="n">
-        <v>52995513.02</v>
+        <v>-101060326.86</v>
       </c>
       <c r="BD105" t="inlineStr">
         <is>
@@ -45535,27 +45535,27 @@
       </c>
       <c r="BE105" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/10/02</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr">
@@ -45570,27 +45570,27 @@
       </c>
       <c r="BL105" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM105" t="inlineStr">
         <is>
-          <t>-19.69180399575732</t>
+          <t>1.179095346377122</t>
         </is>
       </c>
       <c r="BN105" t="inlineStr">
         <is>
-          <t>32.8429209193585</t>
+          <t>9.881236321227592</t>
         </is>
       </c>
       <c r="BO105" t="inlineStr">
         <is>
-          <t>24.67740643280432</t>
+          <t>22.46336360303147</t>
         </is>
       </c>
       <c r="BP105" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ105" t="inlineStr">
@@ -45600,32 +45600,32 @@
       </c>
       <c r="BR105" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="BS105" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT105" t="inlineStr">
         <is>
-          <t>269.64</t>
+          <t>118.80</t>
         </is>
       </c>
       <c r="BU105" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="BV105" t="inlineStr">
         <is>
-          <t>14.33%</t>
+          <t>9.91%</t>
         </is>
       </c>
       <c r="BW105" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="BX105" t="inlineStr">
@@ -45635,52 +45635,52 @@
       </c>
       <c r="BY105" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>171491</t>
         </is>
       </c>
       <c r="BZ105" t="inlineStr">
         <is>
-          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+          <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
         </is>
       </c>
       <c r="CA105" t="inlineStr">
         <is>
-          <t>華碩-電腦及週邊設備業-上市</t>
+          <t>技嘉-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CB105" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CC105" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>271.5</t>
         </is>
       </c>
       <c r="CD105" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>277.0</t>
         </is>
       </c>
       <c r="CE105" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>268.5</t>
         </is>
       </c>
       <c r="CF105" t="inlineStr">
         <is>
-          <t>661.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="CG105" t="inlineStr">
         <is>
-          <t>346.61</t>
+          <t>82.81</t>
         </is>
       </c>
       <c r="CH105" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+          <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
       <c r="CI105" t="inlineStr">
@@ -45697,17 +45697,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2587.128</t>
+          <t>3325.4</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -45717,7 +45717,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -45727,17 +45727,17 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -45747,37 +45747,37 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2025-10-27 00:00:00</t>
+          <t>2025-10-02 00:00:00</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2025-11-03 00:00:00</t>
+          <t>2025-10-14 00:00:00</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>2025-08-11 00:00:00</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2025-09-30 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>714.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -45787,12 +45787,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>289.5</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -45802,27 +45802,27 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>17.67</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
@@ -45833,131 +45833,131 @@
       <c r="AC106" t="inlineStr"/>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.51</t>
         </is>
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>675.4</t>
+          <t>272.1</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>690.9</t>
+          <t>281.08</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>676.56</t>
+          <t>281.6</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>665.72</t>
+          <t>281.66</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>-133.28</t>
+          <t>-84.26</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>-82.95</t>
+          <t>-107.34</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/09/09</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>5203739969.20767</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>1720492718.0</t>
+          <t>907595958.0</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>2044328041.6</t>
+          <t>1275619829.0</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>1858898579.5</t>
+          <t>1172325841.7</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>1901243274.0</t>
+          <t>1645952464.16</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>185429462</t>
+          <t>103293987</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>-4226337.417336328</t>
+          <t>-147182494.5138102</t>
         </is>
       </c>
       <c r="BC106" t="n">
-        <v>44601454.33</v>
+        <v>-97847632.76000001</v>
       </c>
       <c r="BD106" t="inlineStr">
         <is>
@@ -45966,27 +45966,27 @@
       </c>
       <c r="BE106" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/10/02</t>
         </is>
       </c>
       <c r="BG106" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-9.36</t>
         </is>
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BI106" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BJ106" t="inlineStr">
@@ -46001,62 +46001,62 @@
       </c>
       <c r="BL106" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM106" t="inlineStr">
         <is>
-          <t>-19.69180399575732</t>
+          <t>1.179095346377122</t>
         </is>
       </c>
       <c r="BN106" t="inlineStr">
         <is>
-          <t>32.8429209193585</t>
+          <t>9.881236321227592</t>
         </is>
       </c>
       <c r="BO106" t="inlineStr">
         <is>
-          <t>24.67740643280432</t>
+          <t>22.46336360303147</t>
         </is>
       </c>
       <c r="BP106" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ106" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR106" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="BS106" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT106" t="inlineStr">
         <is>
-          <t>269.64</t>
+          <t>118.80</t>
         </is>
       </c>
       <c r="BU106" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="BV106" t="inlineStr">
         <is>
-          <t>14.33%</t>
+          <t>9.91%</t>
         </is>
       </c>
       <c r="BW106" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="BX106" t="inlineStr">
@@ -46066,52 +46066,52 @@
       </c>
       <c r="BY106" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>171491</t>
         </is>
       </c>
       <c r="BZ106" t="inlineStr">
         <is>
-          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+          <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
         </is>
       </c>
       <c r="CA106" t="inlineStr">
         <is>
-          <t>華碩-電腦及週邊設備業-上市</t>
+          <t>技嘉-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CB106" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CC106" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>275.5</t>
         </is>
       </c>
       <c r="CD106" t="inlineStr">
         <is>
-          <t>672.0</t>
+          <t>278.0</t>
         </is>
       </c>
       <c r="CE106" t="inlineStr">
         <is>
-          <t>662.0</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="CF106" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>271.0</t>
         </is>
       </c>
       <c r="CG106" t="inlineStr">
         <is>
-          <t>346.61</t>
+          <t>82.81</t>
         </is>
       </c>
       <c r="CH106" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+          <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
       <c r="CI106" t="inlineStr">
@@ -46128,17 +46128,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>3583.582</t>
+          <t>7203.731</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -46148,7 +46148,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>278.5</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -46158,17 +46158,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-8.79</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -46178,37 +46178,37 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2025-10-27 00:00:00</t>
+          <t>2025-10-02 00:00:00</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2025-11-03 00:00:00</t>
+          <t>2025-10-14 00:00:00</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>2025-08-11 00:00:00</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2025-09-30 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>714.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -46218,12 +46218,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>289.5</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -46233,27 +46233,27 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16.56</t>
+          <t>38.28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
@@ -46264,131 +46264,131 @@
       <c r="AC107" t="inlineStr"/>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>274.0</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>691.6</t>
+          <t>282.85</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>676.06</t>
+          <t>281.73</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>665.44</t>
+          <t>281.73</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>-86.71</t>
+          <t>-109.28</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>-77.27</t>
+          <t>-105.79</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/09/09</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>5203739969.20767</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>2391568906.0</t>
+          <t>1999979629.0</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>2129942802.4</t>
+          <t>1300233451.0</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>1937240022.2</t>
+          <t>1180010364.4</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>1893640408.06</t>
+          <t>1650879347.58</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>192702780</t>
+          <t>120223086</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>-13104117.73556212</t>
+          <t>-156152469.3784109</t>
         </is>
       </c>
       <c r="BC107" t="n">
-        <v>74437497.48999999</v>
+        <v>-75266515.23</v>
       </c>
       <c r="BD107" t="inlineStr">
         <is>
@@ -46397,27 +46397,27 @@
       </c>
       <c r="BE107" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/10/02</t>
         </is>
       </c>
       <c r="BG107" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BI107" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BJ107" t="inlineStr">
@@ -46432,62 +46432,62 @@
       </c>
       <c r="BL107" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM107" t="inlineStr">
         <is>
-          <t>-19.69180399575732</t>
+          <t>1.179095346377122</t>
         </is>
       </c>
       <c r="BN107" t="inlineStr">
         <is>
-          <t>32.8429209193585</t>
+          <t>9.881236321227592</t>
         </is>
       </c>
       <c r="BO107" t="inlineStr">
         <is>
-          <t>24.67740643280432</t>
+          <t>22.46336360303147</t>
         </is>
       </c>
       <c r="BP107" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ107" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR107" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="BS107" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT107" t="inlineStr">
         <is>
-          <t>269.64</t>
+          <t>118.80</t>
         </is>
       </c>
       <c r="BU107" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="BV107" t="inlineStr">
         <is>
-          <t>14.33%</t>
+          <t>9.91%</t>
         </is>
       </c>
       <c r="BW107" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="BX107" t="inlineStr">
@@ -46497,52 +46497,52 @@
       </c>
       <c r="BY107" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>171491</t>
         </is>
       </c>
       <c r="BZ107" t="inlineStr">
         <is>
-          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+          <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
         </is>
       </c>
       <c r="CA107" t="inlineStr">
         <is>
-          <t>華碩-電腦及週邊設備業-上市</t>
+          <t>技嘉-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CB107" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CC107" t="inlineStr">
         <is>
-          <t>678.0</t>
+          <t>270.0</t>
         </is>
       </c>
       <c r="CD107" t="inlineStr">
         <is>
-          <t>678.0</t>
+          <t>284.0</t>
         </is>
       </c>
       <c r="CE107" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>267.5</t>
         </is>
       </c>
       <c r="CF107" t="inlineStr">
         <is>
-          <t>664.0</t>
+          <t>278.5</t>
         </is>
       </c>
       <c r="CG107" t="inlineStr">
         <is>
-          <t>346.61</t>
+          <t>82.81</t>
         </is>
       </c>
       <c r="CH107" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+          <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
       <c r="CI107" t="inlineStr">
@@ -46559,7 +46559,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -46569,7 +46569,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2990.66</t>
+          <t>3417.697</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -46579,7 +46579,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>267.0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -46589,17 +46589,17 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -46609,37 +46609,37 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2025-10-27 00:00:00</t>
+          <t>2025-10-02 00:00:00</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2025-11-03 00:00:00</t>
+          <t>2025-10-14 00:00:00</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>2025-08-11 00:00:00</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2025-09-30 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>714.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -46649,12 +46649,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>289.5</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -46664,27 +46664,27 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>18.16</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
@@ -46695,12 +46695,12 @@
       <c r="AC108" t="inlineStr"/>
       <c r="AD108" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -46715,111 +46715,111 @@
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr">
         <is>
-          <t>687.6</t>
+          <t>274.6</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>693.0</t>
+          <t>284.48</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>675.44</t>
+          <t>281.58</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>665.02</t>
+          <t>281.76</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>-50.69</t>
+          <t>-210.77</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>-72.34</t>
+          <t>-104.21</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/09/09</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>5203739969.20767</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>2035167596.0</t>
+          <t>907028321.0</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>2018014894.0</t>
+          <t>1084771653.2</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>1817621011.7</t>
+          <t>1076044529.9</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>1870325126.16</t>
+          <t>1631138160.78</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>200393882</t>
+          <t>8727123</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>-29020775.04864686</t>
+          <t>-170859006.4958906</t>
         </is>
       </c>
       <c r="BC108" t="n">
-        <v>42500914.08</v>
+        <v>-157360793.69</v>
       </c>
       <c r="BD108" t="inlineStr">
         <is>
@@ -46828,27 +46828,27 @@
       </c>
       <c r="BE108" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/10/02</t>
         </is>
       </c>
       <c r="BG108" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BI108" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BJ108" t="inlineStr">
@@ -46863,62 +46863,62 @@
       </c>
       <c r="BL108" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM108" t="inlineStr">
         <is>
-          <t>-19.69180399575732</t>
+          <t>1.179095346377122</t>
         </is>
       </c>
       <c r="BN108" t="inlineStr">
         <is>
-          <t>32.8429209193585</t>
+          <t>9.881236321227592</t>
         </is>
       </c>
       <c r="BO108" t="inlineStr">
         <is>
-          <t>24.67740643280432</t>
+          <t>22.46336360303147</t>
         </is>
       </c>
       <c r="BP108" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ108" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR108" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BS108" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT108" t="inlineStr">
         <is>
-          <t>269.64</t>
+          <t>118.80</t>
         </is>
       </c>
       <c r="BU108" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="BV108" t="inlineStr">
         <is>
-          <t>14.33%</t>
+          <t>9.91%</t>
         </is>
       </c>
       <c r="BW108" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="BX108" t="inlineStr">
@@ -46928,52 +46928,52 @@
       </c>
       <c r="BY108" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>171491</t>
         </is>
       </c>
       <c r="BZ108" t="inlineStr">
         <is>
-          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+          <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
         </is>
       </c>
       <c r="CA108" t="inlineStr">
         <is>
-          <t>華碩-電腦及週邊設備業-上市</t>
+          <t>技嘉-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CB108" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CC108" t="inlineStr">
         <is>
-          <t>679.0</t>
+          <t>263.0</t>
         </is>
       </c>
       <c r="CD108" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>268.5</t>
         </is>
       </c>
       <c r="CE108" t="inlineStr">
         <is>
-          <t>677.0</t>
+          <t>261.0</t>
         </is>
       </c>
       <c r="CF108" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>267.0</t>
         </is>
       </c>
       <c r="CG108" t="inlineStr">
         <is>
-          <t>346.61</t>
+          <t>82.81</t>
         </is>
       </c>
       <c r="CH108" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+          <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
       <c r="CI108" t="inlineStr">
@@ -46990,17 +46990,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>3424.467</t>
+          <t>6216.935</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -47010,7 +47010,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>267.0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -47020,17 +47020,17 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>14.82</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -47040,37 +47040,37 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2025-10-27 00:00:00</t>
+          <t>2025-10-02 00:00:00</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2025-11-03 00:00:00</t>
+          <t>2025-10-14 00:00:00</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>2025-08-11 00:00:00</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2025-09-30 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>714.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -47080,12 +47080,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>289.5</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -47095,27 +47095,27 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
@@ -47126,12 +47126,12 @@
       <c r="AC109" t="inlineStr"/>
       <c r="AD109" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -47141,116 +47141,116 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
-          <t>693.2</t>
+          <t>278.1</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>693.5</t>
+          <t>286.7</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>674.24</t>
+          <t>281.69</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>664.54</t>
+          <t>281.89</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>-37.33</t>
+          <t>-383.98</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>-68.83</t>
+          <t>-101.99</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/09/09</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>5203739969.20767</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>2312370123.0</t>
+          <t>1682662900.0</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>1946502801.0</t>
+          <t>1123770239.0</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>1695217335.8</t>
+          <t>1110714152.4</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>1857410869.06</t>
+          <t>1628922023.86</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>251285465</t>
+          <t>13056086</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>-42024718.52679587</t>
+          <t>-173313227.0066889</t>
         </is>
       </c>
       <c r="BC109" t="n">
-        <v>33545188.36</v>
+        <v>-151916380.13</v>
       </c>
       <c r="BD109" t="inlineStr">
         <is>
@@ -47259,27 +47259,27 @@
       </c>
       <c r="BE109" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/10/02</t>
         </is>
       </c>
       <c r="BG109" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BI109" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BJ109" t="inlineStr">
@@ -47294,62 +47294,62 @@
       </c>
       <c r="BL109" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM109" t="inlineStr">
         <is>
-          <t>-19.69180399575732</t>
+          <t>1.179095346377122</t>
         </is>
       </c>
       <c r="BN109" t="inlineStr">
         <is>
-          <t>32.8429209193585</t>
+          <t>9.881236321227592</t>
         </is>
       </c>
       <c r="BO109" t="inlineStr">
         <is>
-          <t>24.67740643280432</t>
+          <t>22.46336360303147</t>
         </is>
       </c>
       <c r="BP109" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ109" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR109" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="BS109" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT109" t="inlineStr">
         <is>
-          <t>269.64</t>
+          <t>118.80</t>
         </is>
       </c>
       <c r="BU109" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="BV109" t="inlineStr">
         <is>
-          <t>14.33%</t>
+          <t>9.91%</t>
         </is>
       </c>
       <c r="BW109" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="BX109" t="inlineStr">
@@ -47359,52 +47359,52 @@
       </c>
       <c r="BY109" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>171491</t>
         </is>
       </c>
       <c r="BZ109" t="inlineStr">
         <is>
-          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+          <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
         </is>
       </c>
       <c r="CA109" t="inlineStr">
         <is>
-          <t>華碩-電腦及週邊設備業-上市</t>
+          <t>技嘉-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CB109" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CC109" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>277.0</t>
         </is>
       </c>
       <c r="CD109" t="inlineStr">
         <is>
-          <t>684.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="CE109" t="inlineStr">
         <is>
-          <t>666.0</t>
+          <t>267.0</t>
         </is>
       </c>
       <c r="CF109" t="inlineStr">
         <is>
-          <t>681.0</t>
+          <t>267.0</t>
         </is>
       </c>
       <c r="CG109" t="inlineStr">
         <is>
-          <t>346.61</t>
+          <t>82.81</t>
         </is>
       </c>
       <c r="CH109" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+          <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
       <c r="CI109" t="inlineStr">
@@ -47421,17 +47421,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2544.205</t>
+          <t>3171.091</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -47441,7 +47441,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>277.0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -47451,17 +47451,17 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-12.79</t>
+          <t>-8.2</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>11.80</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -47471,37 +47471,37 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2025-10-27 00:00:00</t>
+          <t>2025-10-02 00:00:00</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2025-11-03 00:00:00</t>
+          <t>2025-10-14 00:00:00</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>2025-08-11 00:00:00</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2025-09-30 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>714.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>691.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -47511,12 +47511,12 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>668.0</t>
+          <t>289.5</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>671.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -47526,27 +47526,27 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
@@ -47557,12 +47557,12 @@
       <c r="AC110" t="inlineStr"/>
       <c r="AD110" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>441</t>
         </is>
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -47572,116 +47572,116 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr">
         <is>
-          <t>698.8</t>
+          <t>282.0</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>693.7</t>
+          <t>288.3</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>673.14</t>
+          <t>281.75</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>664.05</t>
+          <t>282.04</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>-21.44</t>
+          <t>-6296.33</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>-65.92</t>
+          <t>-100.08</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/09/09</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>3298136947.677745</t>
+          <t>5203739969.20767</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>1762040865.0</t>
+          <t>880832337.0</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>1755644235.8</t>
+          <t>1038637740.2</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>1570290079.0</t>
+          <t>1044103559.3</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>1841151084.92</t>
+          <t>1633444942.94</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>185354156</t>
+          <t>-5465819</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>-55764701.59648874</t>
+          <t>-177203562.8020309</t>
         </is>
       </c>
       <c r="BC110" t="n">
-        <v>-10147018.73</v>
+        <v>-221816766.37</v>
       </c>
       <c r="BD110" t="inlineStr">
         <is>
@@ -47690,27 +47690,27 @@
       </c>
       <c r="BE110" t="inlineStr">
         <is>
-          <t>673.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>2025/09/17</t>
+          <t>2025/10/02</t>
         </is>
       </c>
       <c r="BG110" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BI110" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="BJ110" t="inlineStr">
@@ -47725,27 +47725,27 @@
       </c>
       <c r="BL110" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BM110" t="inlineStr">
         <is>
-          <t>-19.69180399575732</t>
+          <t>1.179095346377122</t>
         </is>
       </c>
       <c r="BN110" t="inlineStr">
         <is>
-          <t>32.8429209193585</t>
+          <t>9.881236321227592</t>
         </is>
       </c>
       <c r="BO110" t="inlineStr">
         <is>
-          <t>24.67740643280432</t>
+          <t>22.46336360303147</t>
         </is>
       </c>
       <c r="BP110" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ110" t="inlineStr">
@@ -47755,32 +47755,32 @@
       </c>
       <c r="BR110" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BS110" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="BT110" t="inlineStr">
         <is>
-          <t>269.64</t>
+          <t>118.80</t>
         </is>
       </c>
       <c r="BU110" t="inlineStr">
         <is>
-          <t>13.02</t>
+          <t>14.18</t>
         </is>
       </c>
       <c r="BV110" t="inlineStr">
         <is>
-          <t>14.33%</t>
+          <t>9.91%</t>
         </is>
       </c>
       <c r="BW110" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>4.32%</t>
         </is>
       </c>
       <c r="BX110" t="inlineStr">
@@ -47790,52 +47790,52 @@
       </c>
       <c r="BY110" t="inlineStr">
         <is>
-          <t>453084</t>
+          <t>171491</t>
         </is>
       </c>
       <c r="BZ110" t="inlineStr">
         <is>
-          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+          <t>網路通訊產品64.27%、電腦配件31.22%、其他4.51% (2024年)</t>
         </is>
       </c>
       <c r="CA110" t="inlineStr">
         <is>
-          <t>華碩-電腦及週邊設備業-上市</t>
+          <t>技嘉-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CB110" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右上上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CC110" t="inlineStr">
         <is>
-          <t>698.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="CD110" t="inlineStr">
         <is>
-          <t>705.0</t>
+          <t>280.5</t>
         </is>
       </c>
       <c r="CE110" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>276.0</t>
         </is>
       </c>
       <c r="CF110" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>277.0</t>
         </is>
       </c>
       <c r="CG110" t="inlineStr">
         <is>
-          <t>346.61</t>
+          <t>82.81</t>
         </is>
       </c>
       <c r="CH110" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+          <t>** 電腦及週邊設備 - 顯示器模組、主機板、機殼、電源供應器、散熱片、風扇馬達、散熱模組、顯示卡、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
       <c r="CI110" t="inlineStr">
@@ -47857,12 +47857,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3097.185</t>
+          <t>6416.499</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -47872,72 +47872,72 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
+          <t>610.0</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>-4.15</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>20.69</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>-13.28</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>-4.15</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>7.90</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>2025-10-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>2025-11-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>2025-09-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>714.0</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr">
-        <is>
-          <t>691.0</t>
-        </is>
-      </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>714.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
@@ -47952,12 +47952,12 @@
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-11.72</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
@@ -47967,17 +47967,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>29.66</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
@@ -48003,273 +48003,4583 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>-4.21</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>-6.10</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="AL111" t="inlineStr">
+        <is>
+          <t>636.8</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>678.2</t>
+        </is>
+      </c>
+      <c r="AN111" t="inlineStr">
+        <is>
+          <t>677.46</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>665.81</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>-175.57</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>-14.12</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>-5.12</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr">
+        <is>
+          <t>-122.08</t>
+        </is>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>3298136947.677745</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>3971577357.0</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>3110892215.0</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>2577610128.3</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>2089597881.18</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>533282086</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>112478878.5941267</t>
+        </is>
+      </c>
+      <c r="BC111" t="n">
+        <v>272741488.12</v>
+      </c>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE111" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BF111" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BG111" t="inlineStr">
+        <is>
+          <t>-9.36</t>
+        </is>
+      </c>
+      <c r="BH111" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BI111" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ111" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK111" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL111" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BM111" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BN111" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BO111" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BP111" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ111" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR111" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="BS111" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="BT111" t="inlineStr">
+        <is>
+          <t>269.64</t>
+        </is>
+      </c>
+      <c r="BU111" t="inlineStr">
+        <is>
+          <t>13.02</t>
+        </is>
+      </c>
+      <c r="BV111" t="inlineStr">
+        <is>
+          <t>14.33%</t>
+        </is>
+      </c>
+      <c r="BW111" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="BX111" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="BY111" t="inlineStr">
+        <is>
+          <t>453084</t>
+        </is>
+      </c>
+      <c r="BZ111" t="inlineStr">
+        <is>
+          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA111" t="inlineStr">
+        <is>
+          <t>華碩-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB111" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="CC111" t="inlineStr">
+        <is>
+          <t>637.0</t>
+        </is>
+      </c>
+      <c r="CD111" t="inlineStr">
+        <is>
+          <t>637.0</t>
+        </is>
+      </c>
+      <c r="CE111" t="inlineStr">
+        <is>
+          <t>610.0</t>
+        </is>
+      </c>
+      <c r="CF111" t="inlineStr">
+        <is>
+          <t>610.0</t>
+        </is>
+      </c>
+      <c r="CG111" t="inlineStr">
+        <is>
+          <t>346.61</t>
+        </is>
+      </c>
+      <c r="CH111" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+        </is>
+      </c>
+      <c r="CI111" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3558.4</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>633.0</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-3.77</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>-4.15</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>11.08</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>691.0</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>668.0</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>671.0</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>-8.39</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>16.45</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr"/>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>-2.22</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>-5.07</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>647.4</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>681.95</t>
+        </is>
+      </c>
+      <c r="AN112" t="inlineStr">
+        <is>
+          <t>677.64</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>665.98</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>-270.92</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>-10.66</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>-2.87</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr">
+        <is>
+          <t>-112.39</t>
+        </is>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>3298136947.677745</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>2253776059.0</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>2660675287.2</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>2395309044.8</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>2031062259.28</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>265366242</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>83340222.31716728</t>
+        </is>
+      </c>
+      <c r="BC112" t="n">
+        <v>184622942.89</v>
+      </c>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE112" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BF112" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BG112" t="inlineStr">
+        <is>
+          <t>-5.94</t>
+        </is>
+      </c>
+      <c r="BH112" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BI112" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ112" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK112" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL112" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BM112" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BN112" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BO112" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BP112" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ112" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR112" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="BS112" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="BT112" t="inlineStr">
+        <is>
+          <t>269.64</t>
+        </is>
+      </c>
+      <c r="BU112" t="inlineStr">
+        <is>
+          <t>13.02</t>
+        </is>
+      </c>
+      <c r="BV112" t="inlineStr">
+        <is>
+          <t>14.33%</t>
+        </is>
+      </c>
+      <c r="BW112" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="BX112" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="BY112" t="inlineStr">
+        <is>
+          <t>453084</t>
+        </is>
+      </c>
+      <c r="BZ112" t="inlineStr">
+        <is>
+          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA112" t="inlineStr">
+        <is>
+          <t>華碩-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB112" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="CC112" t="inlineStr">
+        <is>
+          <t>625.0</t>
+        </is>
+      </c>
+      <c r="CD112" t="inlineStr">
+        <is>
+          <t>638.0</t>
+        </is>
+      </c>
+      <c r="CE112" t="inlineStr">
+        <is>
+          <t>625.0</t>
+        </is>
+      </c>
+      <c r="CF112" t="inlineStr">
+        <is>
+          <t>633.0</t>
+        </is>
+      </c>
+      <c r="CG112" t="inlineStr">
+        <is>
+          <t>346.61</t>
+        </is>
+      </c>
+      <c r="CH112" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+        </is>
+      </c>
+      <c r="CI112" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>-2.16</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>5110.97</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>633.0</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-3.77</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>-4.15</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>14.24</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>691.0</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>668.0</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>671.0</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>-8.39</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>23.62</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>-2.53</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr"/>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>-3.15</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>-4.52</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>653.6</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>684.55</t>
+        </is>
+      </c>
+      <c r="AN113" t="inlineStr">
+        <is>
+          <t>677.36</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>666.06</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>-809.67</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>-8.44</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr">
+        <is>
+          <t>-104.00</t>
+        </is>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>3298136947.677745</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>3252501668.0</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>2688233856.6</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>2353124375.3</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>2012331643.46</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>335109481</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>64925182.21223693</t>
+        </is>
+      </c>
+      <c r="BC113" t="n">
+        <v>236195769.4</v>
+      </c>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE113" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BF113" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BG113" t="inlineStr">
+        <is>
+          <t>-5.94</t>
+        </is>
+      </c>
+      <c r="BH113" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BI113" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ113" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK113" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL113" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BM113" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BN113" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BO113" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BP113" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ113" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR113" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="BS113" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="BT113" t="inlineStr">
+        <is>
+          <t>269.64</t>
+        </is>
+      </c>
+      <c r="BU113" t="inlineStr">
+        <is>
+          <t>13.02</t>
+        </is>
+      </c>
+      <c r="BV113" t="inlineStr">
+        <is>
+          <t>14.33%</t>
+        </is>
+      </c>
+      <c r="BW113" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="BX113" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="BY113" t="inlineStr">
+        <is>
+          <t>453084</t>
+        </is>
+      </c>
+      <c r="BZ113" t="inlineStr">
+        <is>
+          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA113" t="inlineStr">
+        <is>
+          <t>華碩-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB113" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="CC113" t="inlineStr">
+        <is>
+          <t>648.0</t>
+        </is>
+      </c>
+      <c r="CD113" t="inlineStr">
+        <is>
+          <t>649.0</t>
+        </is>
+      </c>
+      <c r="CE113" t="inlineStr">
+        <is>
+          <t>633.0</t>
+        </is>
+      </c>
+      <c r="CF113" t="inlineStr">
+        <is>
+          <t>633.0</t>
+        </is>
+      </c>
+      <c r="CG113" t="inlineStr">
+        <is>
+          <t>346.61</t>
+        </is>
+      </c>
+      <c r="CH113" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+        </is>
+      </c>
+      <c r="CI113" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>-2.11</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>6078.152</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-6.07</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>-4.15</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>11.35</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>691.0</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>668.0</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>671.0</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>-6.37</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>28.09</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>-2.47</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr"/>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>-2.44</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>-3.48</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>663.2</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>687.1</t>
+        </is>
+      </c>
+      <c r="AN114" t="inlineStr">
+        <is>
+          <t>677.34</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>666.14</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>-676.47</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>-5.48</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT114" t="inlineStr">
+        <is>
+          <t>-95.91</t>
+        </is>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>3298136947.677745</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>3950855603.0</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>2444767042.2</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>2195634921.6</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>1973519631.2</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>249132120</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>33785075.45068976</t>
+        </is>
+      </c>
+      <c r="BC114" t="n">
+        <v>194429357.4</v>
+      </c>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE114" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BF114" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BG114" t="inlineStr">
+        <is>
+          <t>-3.86</t>
+        </is>
+      </c>
+      <c r="BH114" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BI114" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ114" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK114" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL114" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BM114" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BN114" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BO114" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BP114" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ114" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR114" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="BS114" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="BT114" t="inlineStr">
+        <is>
+          <t>269.64</t>
+        </is>
+      </c>
+      <c r="BU114" t="inlineStr">
+        <is>
+          <t>13.02</t>
+        </is>
+      </c>
+      <c r="BV114" t="inlineStr">
+        <is>
+          <t>14.33%</t>
+        </is>
+      </c>
+      <c r="BW114" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="BX114" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="BY114" t="inlineStr">
+        <is>
+          <t>453084</t>
+        </is>
+      </c>
+      <c r="BZ114" t="inlineStr">
+        <is>
+          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA114" t="inlineStr">
+        <is>
+          <t>華碩-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB114" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="CC114" t="inlineStr">
+        <is>
+          <t>664.0</t>
+        </is>
+      </c>
+      <c r="CD114" t="inlineStr">
+        <is>
+          <t>664.0</t>
+        </is>
+      </c>
+      <c r="CE114" t="inlineStr">
+        <is>
+          <t>646.0</t>
+        </is>
+      </c>
+      <c r="CF114" t="inlineStr">
+        <is>
+          <t>647.0</t>
+        </is>
+      </c>
+      <c r="CG114" t="inlineStr">
+        <is>
+          <t>346.61</t>
+        </is>
+      </c>
+      <c r="CH114" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+        </is>
+      </c>
+      <c r="CI114" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3200.569</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>661.0</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-8.36</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>-4.15</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>691.0</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>668.0</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>671.0</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>-4.34</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>14.79</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>-1.82</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr"/>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>-1.34</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>-2.77</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr">
+        <is>
+          <t>670.0</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>689.1</t>
+        </is>
+      </c>
+      <c r="AN115" t="inlineStr">
+        <is>
+          <t>677.08</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>666.05</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>-219.00</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>-3.04</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT115" t="inlineStr">
+        <is>
+          <t>-88.98</t>
+        </is>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>3298136947.677745</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>2125750388.0</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>2117069946.2</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>1936357091.0</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>1916414460.46</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>180712855</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>4577024.187966792</t>
+        </is>
+      </c>
+      <c r="BC115" t="n">
+        <v>52995513.02</v>
+      </c>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE115" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BF115" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BG115" t="inlineStr">
+        <is>
+          <t>-1.78</t>
+        </is>
+      </c>
+      <c r="BH115" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BI115" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ115" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK115" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL115" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BM115" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BN115" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BO115" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BP115" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ115" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR115" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="BS115" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="BT115" t="inlineStr">
+        <is>
+          <t>269.64</t>
+        </is>
+      </c>
+      <c r="BU115" t="inlineStr">
+        <is>
+          <t>13.02</t>
+        </is>
+      </c>
+      <c r="BV115" t="inlineStr">
+        <is>
+          <t>14.33%</t>
+        </is>
+      </c>
+      <c r="BW115" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="BX115" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="BY115" t="inlineStr">
+        <is>
+          <t>453084</t>
+        </is>
+      </c>
+      <c r="BZ115" t="inlineStr">
+        <is>
+          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA115" t="inlineStr">
+        <is>
+          <t>華碩-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB115" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="CC115" t="inlineStr">
+        <is>
+          <t>668.0</t>
+        </is>
+      </c>
+      <c r="CD115" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="CE115" t="inlineStr">
+        <is>
+          <t>661.0</t>
+        </is>
+      </c>
+      <c r="CF115" t="inlineStr">
+        <is>
+          <t>661.0</t>
+        </is>
+      </c>
+      <c r="CG115" t="inlineStr">
+        <is>
+          <t>346.61</t>
+        </is>
+      </c>
+      <c r="CH115" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+        </is>
+      </c>
+      <c r="CI115" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2587.128</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>663.0</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-8.69</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>-4.15</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>9.98</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>691.0</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>668.0</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>671.0</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>-4.05</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11.96</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>-1.21</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr"/>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>-1.84</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>-2.24</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>675.4</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>690.9</t>
+        </is>
+      </c>
+      <c r="AN116" t="inlineStr">
+        <is>
+          <t>676.56</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>665.72</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>-133.28</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>-1.32</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>3.96</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr">
+        <is>
+          <t>-82.95</t>
+        </is>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>3298136947.677745</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>1720492718.0</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>2044328041.6</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>1858898579.5</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>1901243274.0</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>185429462</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>-4226337.417336328</t>
+        </is>
+      </c>
+      <c r="BC116" t="n">
+        <v>44601454.33</v>
+      </c>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE116" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BF116" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BG116" t="inlineStr">
+        <is>
+          <t>-1.49</t>
+        </is>
+      </c>
+      <c r="BH116" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BI116" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ116" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK116" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL116" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BM116" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BN116" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BO116" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BP116" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ116" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR116" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="BS116" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="BT116" t="inlineStr">
+        <is>
+          <t>269.64</t>
+        </is>
+      </c>
+      <c r="BU116" t="inlineStr">
+        <is>
+          <t>13.02</t>
+        </is>
+      </c>
+      <c r="BV116" t="inlineStr">
+        <is>
+          <t>14.33%</t>
+        </is>
+      </c>
+      <c r="BW116" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="BX116" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="BY116" t="inlineStr">
+        <is>
+          <t>453084</t>
+        </is>
+      </c>
+      <c r="BZ116" t="inlineStr">
+        <is>
+          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA116" t="inlineStr">
+        <is>
+          <t>華碩-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB116" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="CC116" t="inlineStr">
+        <is>
+          <t>670.0</t>
+        </is>
+      </c>
+      <c r="CD116" t="inlineStr">
+        <is>
+          <t>672.0</t>
+        </is>
+      </c>
+      <c r="CE116" t="inlineStr">
+        <is>
+          <t>662.0</t>
+        </is>
+      </c>
+      <c r="CF116" t="inlineStr">
+        <is>
+          <t>663.0</t>
+        </is>
+      </c>
+      <c r="CG116" t="inlineStr">
+        <is>
+          <t>346.61</t>
+        </is>
+      </c>
+      <c r="CH116" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+        </is>
+      </c>
+      <c r="CI116" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>-2.51</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3583.582</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>664.0</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-8.85</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-4.15</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>9.95</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>691.0</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>668.0</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>671.0</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>-3.91</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>16.56</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>-1.96</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr"/>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>-2.50</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="AL117" t="inlineStr">
+        <is>
+          <t>681.0</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>691.6</t>
+        </is>
+      </c>
+      <c r="AN117" t="inlineStr">
+        <is>
+          <t>676.06</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>665.44</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>-86.71</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>5.27</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr">
+        <is>
+          <t>-77.27</t>
+        </is>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>3298136947.677745</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>2391568906.0</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>2129942802.4</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>1937240022.2</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>1893640408.06</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>192702780</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>-13104117.73556212</t>
+        </is>
+      </c>
+      <c r="BC117" t="n">
+        <v>74437497.48999999</v>
+      </c>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE117" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BF117" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BG117" t="inlineStr">
+        <is>
+          <t>-1.34</t>
+        </is>
+      </c>
+      <c r="BH117" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BI117" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ117" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK117" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL117" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BM117" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BN117" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BO117" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BP117" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ117" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR117" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="BS117" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="BT117" t="inlineStr">
+        <is>
+          <t>269.64</t>
+        </is>
+      </c>
+      <c r="BU117" t="inlineStr">
+        <is>
+          <t>13.02</t>
+        </is>
+      </c>
+      <c r="BV117" t="inlineStr">
+        <is>
+          <t>14.33%</t>
+        </is>
+      </c>
+      <c r="BW117" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="BX117" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="BY117" t="inlineStr">
+        <is>
+          <t>453084</t>
+        </is>
+      </c>
+      <c r="BZ117" t="inlineStr">
+        <is>
+          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA117" t="inlineStr">
+        <is>
+          <t>華碩-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB117" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="CC117" t="inlineStr">
+        <is>
+          <t>678.0</t>
+        </is>
+      </c>
+      <c r="CD117" t="inlineStr">
+        <is>
+          <t>678.0</t>
+        </is>
+      </c>
+      <c r="CE117" t="inlineStr">
+        <is>
+          <t>663.0</t>
+        </is>
+      </c>
+      <c r="CF117" t="inlineStr">
+        <is>
+          <t>664.0</t>
+        </is>
+      </c>
+      <c r="CG117" t="inlineStr">
+        <is>
+          <t>346.61</t>
+        </is>
+      </c>
+      <c r="CH117" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+        </is>
+      </c>
+      <c r="CI117" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2990.66</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>681.0</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-11.64</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-4.15</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>11.03</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>691.0</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>668.0</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>671.0</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>13.82</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr"/>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>-0.78</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr">
+        <is>
+          <t>687.6</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>693.0</t>
+        </is>
+      </c>
+      <c r="AN118" t="inlineStr">
+        <is>
+          <t>675.44</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>665.02</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>-50.69</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>6.42</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr">
+        <is>
+          <t>-72.34</t>
+        </is>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>3298136947.677745</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>2035167596.0</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>2018014894.0</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>1817621011.7</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>1870325126.16</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>200393882</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>-29020775.04864686</t>
+        </is>
+      </c>
+      <c r="BC118" t="n">
+        <v>42500914.08</v>
+      </c>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE118" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BF118" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BG118" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BH118" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BI118" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ118" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK118" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL118" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BM118" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BN118" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BO118" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BP118" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ118" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR118" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="BS118" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="BT118" t="inlineStr">
+        <is>
+          <t>269.64</t>
+        </is>
+      </c>
+      <c r="BU118" t="inlineStr">
+        <is>
+          <t>13.02</t>
+        </is>
+      </c>
+      <c r="BV118" t="inlineStr">
+        <is>
+          <t>14.33%</t>
+        </is>
+      </c>
+      <c r="BW118" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="BX118" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="BY118" t="inlineStr">
+        <is>
+          <t>453084</t>
+        </is>
+      </c>
+      <c r="BZ118" t="inlineStr">
+        <is>
+          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA118" t="inlineStr">
+        <is>
+          <t>華碩-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB118" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="CC118" t="inlineStr">
+        <is>
+          <t>679.0</t>
+        </is>
+      </c>
+      <c r="CD118" t="inlineStr">
+        <is>
+          <t>685.0</t>
+        </is>
+      </c>
+      <c r="CE118" t="inlineStr">
+        <is>
+          <t>677.0</t>
+        </is>
+      </c>
+      <c r="CF118" t="inlineStr">
+        <is>
+          <t>681.0</t>
+        </is>
+      </c>
+      <c r="CG118" t="inlineStr">
+        <is>
+          <t>346.61</t>
+        </is>
+      </c>
+      <c r="CH118" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+        </is>
+      </c>
+      <c r="CI118" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3424.467</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>681.0</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-11.64</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>-4.15</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>14.82</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>691.0</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>668.0</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>671.0</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>15.83</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr"/>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>-1.76</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="AL119" t="inlineStr">
+        <is>
+          <t>693.2</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>693.5</t>
+        </is>
+      </c>
+      <c r="AN119" t="inlineStr">
+        <is>
+          <t>674.24</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>664.54</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>-37.33</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>7.23</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr">
+        <is>
+          <t>-68.83</t>
+        </is>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>3298136947.677745</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>2312370123.0</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>1946502801.0</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>1695217335.8</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>1857410869.06</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>251285465</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>-42024718.52679587</t>
+        </is>
+      </c>
+      <c r="BC119" t="n">
+        <v>33545188.36</v>
+      </c>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE119" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BF119" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BG119" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="BH119" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BI119" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ119" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK119" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL119" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BM119" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BN119" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BO119" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BP119" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ119" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR119" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="BS119" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="BT119" t="inlineStr">
+        <is>
+          <t>269.64</t>
+        </is>
+      </c>
+      <c r="BU119" t="inlineStr">
+        <is>
+          <t>13.02</t>
+        </is>
+      </c>
+      <c r="BV119" t="inlineStr">
+        <is>
+          <t>14.33%</t>
+        </is>
+      </c>
+      <c r="BW119" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="BX119" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="BY119" t="inlineStr">
+        <is>
+          <t>453084</t>
+        </is>
+      </c>
+      <c r="BZ119" t="inlineStr">
+        <is>
+          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA119" t="inlineStr">
+        <is>
+          <t>華碩-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB119" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="CC119" t="inlineStr">
+        <is>
+          <t>684.0</t>
+        </is>
+      </c>
+      <c r="CD119" t="inlineStr">
+        <is>
+          <t>684.0</t>
+        </is>
+      </c>
+      <c r="CE119" t="inlineStr">
+        <is>
+          <t>666.0</t>
+        </is>
+      </c>
+      <c r="CF119" t="inlineStr">
+        <is>
+          <t>681.0</t>
+        </is>
+      </c>
+      <c r="CG119" t="inlineStr">
+        <is>
+          <t>346.61</t>
+        </is>
+      </c>
+      <c r="CH119" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+        </is>
+      </c>
+      <c r="CI119" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2544.205</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>688.0</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-12.79</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>-4.15</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>11.80</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>691.0</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>668.0</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>671.0</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>11.76</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>-2.33</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr"/>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>-1.55</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="AL120" t="inlineStr">
+        <is>
+          <t>698.8</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>693.7</t>
+        </is>
+      </c>
+      <c r="AN120" t="inlineStr">
+        <is>
+          <t>673.14</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>664.05</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>-21.44</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>7.91</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>23.2</t>
+        </is>
+      </c>
+      <c r="AT120" t="inlineStr">
+        <is>
+          <t>-65.92</t>
+        </is>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>3298136947.677745</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>1762040865.0</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>1755644235.8</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>1570290079.0</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>1841151084.92</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>185354156</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>-55764701.59648874</t>
+        </is>
+      </c>
+      <c r="BC120" t="n">
+        <v>-10147018.73</v>
+      </c>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE120" t="inlineStr">
+        <is>
+          <t>673.0</t>
+        </is>
+      </c>
+      <c r="BF120" t="inlineStr">
+        <is>
+          <t>2025/09/17</t>
+        </is>
+      </c>
+      <c r="BG120" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="BH120" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BI120" t="inlineStr">
+        <is>
+          <t>華碩</t>
+        </is>
+      </c>
+      <c r="BJ120" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK120" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL120" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="BM120" t="inlineStr">
+        <is>
+          <t>-19.69180399575732</t>
+        </is>
+      </c>
+      <c r="BN120" t="inlineStr">
+        <is>
+          <t>32.8429209193585</t>
+        </is>
+      </c>
+      <c r="BO120" t="inlineStr">
+        <is>
+          <t>24.67740643280432</t>
+        </is>
+      </c>
+      <c r="BP120" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ120" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR120" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="BS120" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="BT120" t="inlineStr">
+        <is>
+          <t>269.64</t>
+        </is>
+      </c>
+      <c r="BU120" t="inlineStr">
+        <is>
+          <t>13.02</t>
+        </is>
+      </c>
+      <c r="BV120" t="inlineStr">
+        <is>
+          <t>14.33%</t>
+        </is>
+      </c>
+      <c r="BW120" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
+      <c r="BX120" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="BY120" t="inlineStr">
+        <is>
+          <t>453084</t>
+        </is>
+      </c>
+      <c r="BZ120" t="inlineStr">
+        <is>
+          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA120" t="inlineStr">
+        <is>
+          <t>華碩-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB120" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上市</t>
+        </is>
+      </c>
+      <c r="CC120" t="inlineStr">
+        <is>
+          <t>698.0</t>
+        </is>
+      </c>
+      <c r="CD120" t="inlineStr">
+        <is>
+          <t>705.0</t>
+        </is>
+      </c>
+      <c r="CE120" t="inlineStr">
+        <is>
+          <t>687.0</t>
+        </is>
+      </c>
+      <c r="CF120" t="inlineStr">
+        <is>
+          <t>688.0</t>
+        </is>
+      </c>
+      <c r="CG120" t="inlineStr">
+        <is>
+          <t>346.61</t>
+        </is>
+      </c>
+      <c r="CH120" t="inlineStr">
+        <is>
+          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
+        </is>
+      </c>
+      <c r="CI120" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>-0.87</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3097.185</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>691.0</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-13.28</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>-4.15</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>7.90</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2025-10-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>2025-11-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>2025-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>691.0</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>714.0</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>668.0</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>671.0</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>6.41</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>14.31</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>-1.30</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr"/>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>6416</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
           <t>40.68</t>
         </is>
       </c>
-      <c r="AH111" t="inlineStr">
+      <c r="AH121" t="inlineStr">
         <is>
           <t>-1.71</t>
         </is>
       </c>
-      <c r="AI111" t="inlineStr">
+      <c r="AI121" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="AJ111" t="inlineStr">
+      <c r="AJ121" t="inlineStr">
         <is>
           <t>3.22</t>
         </is>
       </c>
-      <c r="AK111" t="inlineStr">
+      <c r="AK121" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="AL111" t="inlineStr">
+      <c r="AL121" t="inlineStr">
         <is>
           <t>703.0</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
+      <c r="AM121" t="inlineStr">
         <is>
           <t>693.5</t>
         </is>
       </c>
-      <c r="AN111" t="inlineStr">
+      <c r="AN121" t="inlineStr">
         <is>
           <t>671.88</t>
         </is>
       </c>
-      <c r="AO111" t="inlineStr">
+      <c r="AO121" t="inlineStr">
         <is>
           <t>663.46</t>
         </is>
       </c>
-      <c r="AP111" t="inlineStr">
+      <c r="AP121" t="inlineStr">
         <is>
           <t>-9.35</t>
         </is>
       </c>
-      <c r="AQ111" t="inlineStr">
+      <c r="AQ121" t="inlineStr">
         <is>
           <t>7.55</t>
         </is>
       </c>
-      <c r="AR111" t="inlineStr">
+      <c r="AR121" t="inlineStr">
         <is>
           <t>8.33</t>
         </is>
       </c>
-      <c r="AS111" t="inlineStr">
+      <c r="AS121" t="inlineStr">
         <is>
           <t>23.2</t>
         </is>
       </c>
-      <c r="AT111" t="inlineStr">
+      <c r="AT121" t="inlineStr">
         <is>
           <t>-64.10</t>
         </is>
       </c>
-      <c r="AU111" t="inlineStr">
+      <c r="AU121" t="inlineStr">
         <is>
           <t>2025/10/27</t>
         </is>
       </c>
-      <c r="AV111" t="inlineStr">
+      <c r="AV121" t="inlineStr">
         <is>
           <t>3298136947.677745</t>
         </is>
       </c>
-      <c r="AW111" t="inlineStr">
+      <c r="AW121" t="inlineStr">
         <is>
           <t>2148566522.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
+      <c r="AX121" t="inlineStr">
         <is>
           <t>1673469117.4</t>
         </is>
       </c>
-      <c r="AY111" t="inlineStr">
+      <c r="AY121" t="inlineStr">
         <is>
           <t>1550878924.7</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
+      <c r="AZ121" t="inlineStr">
         <is>
           <t>1859076743.5</t>
         </is>
       </c>
-      <c r="BA111" t="inlineStr">
+      <c r="BA121" t="inlineStr">
         <is>
           <t>122590192</t>
         </is>
       </c>
-      <c r="BB111" t="inlineStr">
+      <c r="BB121" t="inlineStr">
         <is>
           <t>-64058825.754549</t>
         </is>
       </c>
-      <c r="BC111" t="n">
+      <c r="BC121" t="n">
         <v>-13238214.82</v>
       </c>
-      <c r="BD111" t="inlineStr">
+      <c r="BD121" t="inlineStr">
         <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="BE111" t="inlineStr">
+      <c r="BE121" t="inlineStr">
         <is>
           <t>673.0</t>
         </is>
       </c>
-      <c r="BF111" t="inlineStr">
+      <c r="BF121" t="inlineStr">
         <is>
           <t>2025/09/17</t>
         </is>
       </c>
-      <c r="BG111" t="inlineStr">
+      <c r="BG121" t="inlineStr">
         <is>
           <t>2.67</t>
         </is>
       </c>
-      <c r="BH111" t="inlineStr">
+      <c r="BH121" t="inlineStr">
         <is>
           <t>華碩</t>
         </is>
       </c>
-      <c r="BI111" t="inlineStr">
+      <c r="BI121" t="inlineStr">
         <is>
           <t>華碩</t>
         </is>
       </c>
-      <c r="BJ111" t="inlineStr">
+      <c r="BJ121" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK111" t="inlineStr">
+      <c r="BK121" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL111" t="inlineStr">
+      <c r="BL121" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="BM111" t="inlineStr">
+      <c r="BM121" t="inlineStr">
         <is>
           <t>-19.69180399575732</t>
         </is>
       </c>
-      <c r="BN111" t="inlineStr">
+      <c r="BN121" t="inlineStr">
         <is>
           <t>32.8429209193585</t>
         </is>
       </c>
-      <c r="BO111" t="inlineStr">
+      <c r="BO121" t="inlineStr">
         <is>
           <t>24.67740643280432</t>
         </is>
       </c>
-      <c r="BP111" t="inlineStr">
+      <c r="BP121" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ111" t="inlineStr">
+      <c r="BQ121" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR111" t="inlineStr">
+      <c r="BR121" t="inlineStr">
         <is>
           <t>1.99</t>
         </is>
       </c>
-      <c r="BS111" t="inlineStr">
+      <c r="BS121" t="inlineStr">
         <is>
           <t>5.57</t>
         </is>
       </c>
-      <c r="BT111" t="inlineStr">
+      <c r="BT121" t="inlineStr">
         <is>
           <t>269.64</t>
         </is>
       </c>
-      <c r="BU111" t="inlineStr">
+      <c r="BU121" t="inlineStr">
         <is>
           <t>13.02</t>
         </is>
       </c>
-      <c r="BV111" t="inlineStr">
+      <c r="BV121" t="inlineStr">
         <is>
           <t>14.33%</t>
         </is>
       </c>
-      <c r="BW111" t="inlineStr">
+      <c r="BW121" t="inlineStr">
         <is>
           <t>4.91%</t>
         </is>
       </c>
-      <c r="BX111" t="inlineStr">
+      <c r="BX121" t="inlineStr">
         <is>
           <t>23.47</t>
         </is>
       </c>
-      <c r="BY111" t="inlineStr">
+      <c r="BY121" t="inlineStr">
         <is>
           <t>453084</t>
         </is>
       </c>
-      <c r="BZ111" t="inlineStr">
+      <c r="BZ121" t="inlineStr">
         <is>
           <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA111" t="inlineStr">
+      <c r="CA121" t="inlineStr">
         <is>
           <t>華碩-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CB111" t="inlineStr">
+      <c r="CB121" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右上上市</t>
         </is>
       </c>
-      <c r="CC111" t="inlineStr">
+      <c r="CC121" t="inlineStr">
         <is>
           <t>692.0</t>
         </is>
       </c>
-      <c r="CD111" t="inlineStr">
+      <c r="CD121" t="inlineStr">
         <is>
           <t>702.0</t>
         </is>
       </c>
-      <c r="CE111" t="inlineStr">
+      <c r="CE121" t="inlineStr">
         <is>
           <t>689.0</t>
         </is>
       </c>
-      <c r="CF111" t="inlineStr">
+      <c r="CF121" t="inlineStr">
         <is>
           <t>691.0</t>
         </is>
       </c>
-      <c r="CG111" t="inlineStr">
+      <c r="CG121" t="inlineStr">
         <is>
           <t>346.61</t>
         </is>
       </c>
-      <c r="CH111" t="inlineStr">
+      <c r="CH121" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
         </is>
       </c>
-      <c r="CI111" t="inlineStr">
+      <c r="CI121" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/顯示卡.xlsx
+++ b/Result/checksun_type/顯示卡.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>45.06</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>48.44</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>51.59</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>51.59</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>3940.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4402.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4402</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>6323.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>39184.18</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>39184.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-3909.263703600152</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>3940</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>3940.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>44.91</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>49.02</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>51.58</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>51.58</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>2447.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4659.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4659</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>7018.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>39493.12</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>39493.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-4163.683925354684</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>2447</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2447.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>44.95999999999999</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>49.59</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>51.49</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>51.49</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>6971.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>5967.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>5967.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>7930.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>39526.6</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>39526.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-4218.474101955635</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>6971</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>6971.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>45.31</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>50.16</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>51.4</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>5066.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>6322.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>6322.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>8508.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>39448.72</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>39448.72</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-4630.800279172861</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>5066</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>5066.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>45.86</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>50.78</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>51.32</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>50.78</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>51.32</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>3586.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>7077.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>7077.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>9305.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>39382.82</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>39382.82</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-4850.344808084155</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>3586</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>3586.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>46.39</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>51.22</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>51.22</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>5225.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>8244.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>8244.200000000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>10922.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>39351.24</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>39351.24</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-4832.181820525857</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>5225</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>5225.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>47.18</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>52.01</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>51.13</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>52.01</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>51.13</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>8989.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>9377.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>9377.200000000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>17686.1</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>39290.08</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>39290.08</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-4809.263916138076</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>8989</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>8989.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>47.62</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>52.58</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>51.04</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>52.58</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>51.04</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>8747.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>9894.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>9894.200000000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>18290.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>39135.9</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>39135.9</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-5008.050341436317</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>8747</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>8747.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>47.98</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>53.01</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>50.92</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>8841.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>10694.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>10694.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>19462.5</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>39000.66</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>39000.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-5087.243436811077</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>8841</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>8841.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>48.25</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>53.48</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>50.79</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>53.48</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>50.79</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>9419.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>11533.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>11533.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>23274.8</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>38917.26</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>38917.26</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-5028.760593174626</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>9419</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>9419.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>48.43</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>53.86</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>50.66</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>50.66</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>10890.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>13601.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>13601.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>23466.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>38779.9</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>38779.9</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-4827.543652509172</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>10890</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>10890.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>64.98</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>70.57</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>77.91</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>77.91</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>14440.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>20248.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>20248</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>24342.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>83648.54</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>83648.53999999999</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-6498.399258858575</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>14440</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>14440.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>64.64</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>71.36</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>78.17</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>71.36</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>78.17</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>24071.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>21063.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>21063.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>24973.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>87968.22</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>87968.22</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-6448.589263125443</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>24071</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>24071.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>64.67999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>72.1</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>78.45</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>78.45</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>32330.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>20817.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>20817.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>25696.4</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>88580.28</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>88580.28</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-7179.018224109343</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>32330</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>32330.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>65.34</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>73.04</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>78.72</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>73.04000000000001</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>78.72</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>19890.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>23556.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>23556.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>24414.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>88503.74</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>88503.74000000001</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-8850.987517511006</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>19890</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>19890.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>66.6</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>73.96</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>79.03</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>73.95999999999999</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>79.03</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>10509.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>27228.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>27228.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>24641.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>88926.62</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>88926.62</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-9590.551239602271</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>10509</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>10509.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>67.8</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>74.79</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>79.26</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>74.79000000000001</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>79.26000000000001</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>18519.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>28437.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>28437</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>26764.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>89466.98</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>89466.98</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-9299.444012604003</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>18519</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>18519.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>69.32000000000001</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>75.59</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>79.5</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>75.59</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>79.5</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>22838.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>28883.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>28883.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>29999.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>89926.84</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>89926.84</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-9409.667830727769</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>22838</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>22838.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>70.36</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>76.29</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>79.75</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>76.29000000000001</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>79.75</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>46028.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>30575.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>30575.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>30583.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>91090.28</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>91090.28</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-9693.820862664295</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>46028</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>46028.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>71.60000000000001</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>77.02</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>79.98</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>77.02</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>79.98</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>38250.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>25273.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>25273</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>28352.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>93285.46</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>93285.46000000001</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-12238.18873462132</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>38250</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>38250.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>72.28</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>77.65</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>80.06</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>80.06</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>16550.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>22053.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>22053.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>31261.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>92957.46</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>92957.46000000001</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-14602.56466832346</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>16550</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>16550.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>72.72</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>78.16</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>80.11</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>78.16</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>80.11</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>20750.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>25092.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>25092</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>34192.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>93074.84</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>93074.84</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-15133.72440688638</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>20750</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>20750.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>70.2</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>73.05</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>69.14</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>73.05</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>69.14</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>33572.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>33291.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>33291.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>79907.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>52563.6</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>52563.6</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-8451.833814836384</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>33572</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>33572.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>69.84</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>73.08</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>68.96</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>73.08</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>68.95999999999999</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>23968.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>35206.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>35206.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>78572.9</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>52193.48</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>52193.48</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-7285.714174139335</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>23968</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>23968.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>69.86</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>73.16</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>68.81</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>73.16</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>68.81</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>18778.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>49174.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>49174.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>80723.8</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>51860.5</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>51860.5</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-4330.624895495712</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>18778</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>18778.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>71.06</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>73.26</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>68.69</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>73.26000000000001</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>68.69</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>41249.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>126334.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>126334.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>84751.5</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>51658.1</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>51658.1</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>601.6678202628682</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>41249</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>41249.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>72.34</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>73.44</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>68.61</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>68.61</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>48891.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>126537.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>126537</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>90533.7</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>50941.56</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>50941.56</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>5218.704992051455</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>48891</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>48891.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>72.91999999999999</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>73.49</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>68.47</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>73.48999999999999</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>68.47</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>43146.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>126523.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>126523.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>110266.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>50056.24</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>50056.24</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>10809.30434489046</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>43146</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>43146.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>73.17999999999999</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>73.4</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>68.33</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>93810.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>121939.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>121939.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>111374.5</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>49406.96</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>49406.96</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>19025.36397948582</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>93810</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>93810.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>73.62</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>73.16</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>68.19</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>73.16</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>68.19</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>404577.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>112272.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>112272.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>106038.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>47927.76</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>47927.76</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>24654.82902964039</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>404577</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>404577.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>73.38000000000001</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>72.71</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>68.0</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>72.70999999999999</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>68</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>42261.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>43168.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>43168.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>71541.8</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>40084.32</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>40084.32</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-1480.071935483087</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>42261</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>42261.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>73.2</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>72.32</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>67.81</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>67.81</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>48823.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>54530.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>54530.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>71688.6</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>39731.78</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>39731.78</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>56.78639775064221</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>48823</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>48823.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>72.96</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>71.85</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>67.68</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>67.68000000000001</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>20226.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>94009.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>94009.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>77244.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>38919.48</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>38919.48</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>1547.198788164882</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>20226</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>20226.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>54.66</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>53.32</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>149413.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>217717.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>217717</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>367044.8</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>237158.66</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>237158.66</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-21084.67091178865</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>149413</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>149413.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>56.04</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>52.92</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>49.09</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>216732.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>231160.8</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>231160.8</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>420206.6</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>235339.22</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>235339.22</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-10587.49947517022</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>216732</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>216732.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>57.18000000000001</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>221658.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>259217.6</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>259217.6</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>453682.5</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>233052.36</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>233052.36</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-2426.165298745036</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>221658</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>221658.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>58.98</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>48.48</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>301588.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>336883.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>336883.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>450728.0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>229641.16</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>229641.16</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>8791.746571103286</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>301588</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>301588.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>60.52</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>48.2</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>199194.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>396703.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>396703.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>425530.3</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>224069.9</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>224069.9</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>15939.41543620441</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>199194</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>199194.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>60.77999999999999</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>51.93</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>216632.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>516372.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>516372.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>418795.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>220937.42</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>220937.42</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>36551.8918350559</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>216632</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>216632.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>47.4</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>357016.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>609252.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>609252.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>418153.5</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>218290.42</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>218290.42</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>62824.50483930594</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>357016</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>357016.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>46.95</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>609988.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>648147.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>648147.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>393131.5</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>212611.62</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>212611.62</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>83071.93395825941</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>609988</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>609988.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>55.94</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>50.29</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>46.43</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>600689.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>564572.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>564572.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>357656.0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>201223.44</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>201223.44</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>81925.83505825518</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>600689</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>600689.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>53.16</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>49.91</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>797538.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>454356.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>454356.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>315081.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>191580.74</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>191580.74</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>78358.94966331136</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>797538</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>797538.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>50.62</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>681031.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>321219.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>321219</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>255754.6</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>176809.8</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>176809.8</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>49373.9008968448</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>681031</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>681031.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>245.9</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>282.15</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>286.24</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>282.15</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>286.24</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>181496538.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>248712009.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>248712009.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>295583263.9</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>404415989.88</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>404415989.88</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-36865543.57806414</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>181496538</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>181496538.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>243.7</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>286.4</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>287.62</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>286.4</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>287.62</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>326035900.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>303753353.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>303753353.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>308503858.9</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>444892029.6</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>444892029.6</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-31426505.93227613</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>326035900</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>326035900.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>242.9</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>290.23</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>288.95</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>290.23</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>288.95</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>131381608.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>344648291.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>344648291.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>305244759.9</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>486354631.84</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>486354631.84</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-38020437.15499777</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>131381608</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>131381608.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>248.1</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>294.2</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>289.92</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>294.2</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>289.92</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>191628215.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>361404158.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>361404158.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>314017182.3</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>492826395.88</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>492826395.88</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-25226649.14620733</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>191628215</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>191628215.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>255.9</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>297.35</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>290.45</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>297.35</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>290.45</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>413017787.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>370339106.6</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>370339106.6</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>343302605.5</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>491927087.64</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>491927087.64</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-12503850.98557067</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>413017787</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>413017787.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>262.8</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>299.42</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>290.68</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>299.42</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>290.68</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>456703259.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>342454518.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>342454518.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>329501632.1</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>487045635.88</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>487045635.88</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-17602170.22089082</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>456703259</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>456703259.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>271.1</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>302.12</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>291.04</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>302.12</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>291.04</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>530510587.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>313254364.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>313254364</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>318010950.7</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>482171320.06</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>482171320.06</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-28937420.76345921</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>530510587</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>530510587.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>279.8</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>304.35</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>291.39</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>304.35</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>291.39</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>215160943.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>265841228.6</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>265841228.6</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>296018261.7</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>474035134.12</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>474035134.12</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-52005084.51129037</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>215160943</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>215160943.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>285.6</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>305.35</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>291.28</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>305.35</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>291.28</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>236302957.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>266630206.4</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>266630206.4</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>300487017.0</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>472138847.46</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>472138847.46</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-49314103.56136036</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>236302957</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>236302957.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>290.8</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>306.1</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>291.06</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>306.1</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>291.06</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>273594845.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>316266104.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>316266104.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>321700457.7</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>472162353.72</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>472162353.72</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-45973842.86284024</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>273594845</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>273594845.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>298.5</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>306.35</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>290.96</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>306.35</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>290.96</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>310702488.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>316548746.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>316548746</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>396274780.2</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>469508914.58</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>469508914.58</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-43555678.33413863</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>310702488</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>310702488.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>52.66</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>59.14</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>61.98</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>59.14</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>61.98</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>19370245.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>16724922.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>16724922.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>29736079.9</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>59920226.2</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>59920226.2</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-7654864.406155422</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>19370245</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>19370245.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>52.4</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>59.83</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>62.09</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>59.83</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>62.09</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>11627684.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>17947425.8</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>17947425.8</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>29554414.4</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>59980908.68</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>59980908.68</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-8179897.695759896</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>11627684</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>11627684.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>52.22000000000001</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>60.59</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>62.24</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>60.59</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>62.24</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>8231015.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>24035589.8</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>24035589.8</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>33395445.3</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>60054884.02</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>60054884.02</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-7808245.941774867</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>8231015</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>8231015.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>52.56</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>61.45</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>61.45</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>62.4</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>20875162.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>41337116.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>41337116.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>34879692.4</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>60292638.06</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>60292638.06</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-6634520.116732866</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>20875162</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>20875162.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>53.9</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>62.33</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>62.58</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>62.33</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>62.58</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>23520508.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>43669028.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>43669028.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>35113728.9</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>60099849.48</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>60099849.48</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-6075551.826789543</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>23520508</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>23520508.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>55.48</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>63.26</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>62.74</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>63.26</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>62.74</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>25482760.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>42747237.0</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>42747237</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>35341328.1</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>59951906.28</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>59951906.28</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-5343471.633056603</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>25482760</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>25482760.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>57.16</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>64.16</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>62.9</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>64.16</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>62.9</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>42068504.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>41161403.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>41161403</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>36260327.6</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>59925738.76</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>59925738.76</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-4317045.797971807</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>42068504</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>42068504.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>58.94000000000001</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>65.18</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>63.1</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>65.18000000000001</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>63.1</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>94738649.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>42755300.8</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>42755300.8</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>40238517.9</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>59413146.08</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>59413146.08</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-4473586.969351687</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>94738649</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>94738649.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>60.72000000000001</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>66.24</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>63.25</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>63.25</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>32534721.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>28422268.2</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>28422268.2</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>43417093.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>58054167.8</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>58054167.8</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-10180676.07241751</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>32534721</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>32534721.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>61.34</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>67.29</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>63.35</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>67.29000000000001</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>63.35</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>18911551.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>26558429.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>26558429.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>42703332.8</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>58228467.96</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>58228467.96</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-11305358.35992521</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>18911551</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>18911551.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>61.82000000000001</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>67.95</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>63.45</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>63.45</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>17553590.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>27935419.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>27935419.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>45075687.4</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>58337032.66</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>58337032.66</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-11048659.18636745</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>17553590</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>17553590.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>27.71</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>28.64</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>30.14</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>28.64</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>30.14</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>2480416.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>5669159.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>5669159</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>7523317.0</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>11539393.26</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>11539393.26</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-818474.2991896216</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>2480416</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>2480416.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>27.42</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>28.71</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>30.21</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>30.21</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>9273710.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>6266386.8</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>6266386.8</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>7766590.3</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>12127429.32</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>12127429.32</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-495704.122365227</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>9273710</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>9273710.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>27.37</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>28.81</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>30.29</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>30.29</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>5111570.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>6195469.4</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>6195469.4</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>7595755.8</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>12312348.14</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>12312348.14</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-744753.0796744758</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>5111570</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>5111570.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>27.64</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>28.97</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>28.97</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>30.4</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>7917211.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>8752684.0</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>8752684</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>8321127.7</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>12449921.88</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>12449921.88</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-627995.408699315</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>7917211</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>7917211.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>28.07</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>30.51</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>30.51</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>3562888.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>8313370.0</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>8313370</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>8256417.8</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>12455611.22</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>12455611.22</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-739374.7212812528</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>3562888</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>3562888.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>30.6</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>5466555.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>9377475.0</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>9377475</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>8207132.7</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>12531282.2</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>12531282.2</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-405547.1777811181</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>5466555</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>5466555.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>28.91</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>29.46</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>30.7</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>8919123.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>9266793.8</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>9266793.800000001</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>8306502.2</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>12573685.9</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>12573685.9</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-118131.1807173137</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>8919123</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>8919123.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>29.09</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>29.55</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>30.78</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>30.78</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>17897643.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>8996042.2</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>8996042.199999999</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>8174931.3</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>12624288.98</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>12624288.98</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-73235.9284576904</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>17897643</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>17897643.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>29.22</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>30.85</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>5720641.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>7889571.4</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>7889571.4</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>7152618.9</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>12409010.28</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>12409010.28</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-968468.5706418827</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>5720641</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>5720641.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>29.08</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>29.66</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>30.91</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>29.66</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>30.91</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>8883413.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>8199465.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>8199465.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>7536702.5</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>12725022.16</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>12725022.16</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-908105.3962392323</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>8883413</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>8883413.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>29.0</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>30.99</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>30.99</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>4913149.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>7036790.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>7036790.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>7710156.9</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>13015869.86</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>13015869.86</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-1128308.382941189</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>4913149</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>4913149.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>35.66</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>36.8</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>39.45</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>39.45</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>9483731.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>8003728.4</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>8003728.4</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>11432871.3</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>19976354.0</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>19976354</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-1642700.774837006</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>9483731</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>9483731.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>35.32000000000001</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>36.96</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>39.58</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>39.58</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>5444278.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>8640591.6</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>8640591.6</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>11527352.8</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>21053187.58</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>21053187.58</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-1816551.593726834</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>5444278</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>5444278.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>35.23</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>37.17</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>39.77</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>39.77</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>5229753.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>10324874.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>10324874</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>13264645.3</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>21830169.94</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>21830169.94</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-1567234.528079201</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>5229753</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>5229753.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>35.47</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>37.42</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>39.95</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>37.42</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>39.95</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>9857706.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>12336112.4</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>12336112.4</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>13554670.5</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>22806012.14</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>22806012.14</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-1132109.808294039</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>9857706</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>9857706.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>35.67</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>37.7</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>40.16</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>40.16</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>10003174.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>13686560.2</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>13686560.2</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>14633551.8</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>23455416.94</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>23455416.94</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-965922.6797333062</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>10003174</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>10003174.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>35.87</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>37.98</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>40.33</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>40.33</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>12668047.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>14862014.2</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>14862014.2</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>15252840.6</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>23993501.14</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>23993501.14</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-709601.1146560721</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>12668047</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>12668047.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>36.27</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>38.29</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>40.52</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>40.52</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>13865690.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>14414114.0</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>14414114</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>15082886.5</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>24849592.38</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>24849592.38</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-603606.6604508758</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>13865690</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>13865690.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>36.63</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>38.54</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>40.73</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>40.73</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>15285945.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>16204416.6</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>16204416.6</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>15694340.1</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>25686050.3</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>25686050.3</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-558947.5237130653</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>15285945</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>15285945.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>36.67</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>38.73</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>40.89</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>40.89</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>16609945.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>14773228.6</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>14773228.6</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>15259342.9</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>26747097.02</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>26747097.02</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-627356.5239550117</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>16609945</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>16609945.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>36.81</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>38.95</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>41.08</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>41.08</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>15880444.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>15580543.4</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>15580543.4</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>14428243.9</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>29041976.96</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>29041976.96</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-844535.2198736854</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>15880444</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>15880444.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>36.88</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>39.09</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>41.25</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>41.25</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>10428546.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>15643667.0</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>15643667</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>14246409.3</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>30828566.88</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>30828566.88</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-1046467.706190588</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>10428546</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>10428546.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>104.4</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>106.52</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>111.25</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>106.52</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>111.25</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>777509323.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>2934553867.8</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>2934553867.8</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>2158280166.7</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>1031583879.48</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>1031583879.48</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>292289650.0664442</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>777509323</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>777509323.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>103.1</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>106.72</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>111.58</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>106.72</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>111.58</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>1668288090.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>3096742737.0</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>3096742737</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>2135464180.0</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>1032124146.48</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>1032124146.48</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>494196663.578167</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>1668288090</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>1668288090.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>102.2</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>106.75</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>111.97</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>111.97</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>8321088018.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>3093155396.4</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>3093155396.4</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>2053773215.2</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>1018612141.58</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>1018612141.58</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>669544791.2885513</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>8321088018</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>8321088018.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>102.2</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>107.08</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>112.51</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>107.08</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>112.51</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>2053070263.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>1728650118.4</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>1728650118.4</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>1347672905.7</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>859682136.04</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>859682136.04</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>183329810.3287945</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>2053070263</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>2053070263.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>103.1</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>107.42</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>113.07</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>107.42</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>113.07</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>1852813645.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>1591834282.6</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>1591834282.6</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>1344225255.8</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>824134046.86</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>824134046.86</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>153762818.0531137</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>1852813645</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>1852813645.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>104.4</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>107.78</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>113.6</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>107.78</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>113.6</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>1588453669.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>1382006465.6</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>1382006465.6</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>1235144843.6</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>792783654.98</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>792783654.98</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>127488794.657387</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>1588453669</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>1588453669.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>106.1</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>108.18</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>114.16</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>108.18</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>114.16</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>1650351387.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>1174185623.0</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>1174185623</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>1167188797.5</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>769923303.52</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>769923303.52</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>113725587.4257281</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>1650351387</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>1650351387.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>107.3</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>108.48</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>114.65</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>108.48</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>114.65</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>1498561628.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>1014391034.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>1014391034</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>1102417113.0</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>744968122.94</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>744968122.9400001</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>83370336.32958221</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>1498561628</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>1498561628.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>109.2</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>108.75</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>115.15</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>115.15</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>1368991084.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>966695693.0</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>966695693</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>1018447736.5</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>725784218.34</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>725784218.34</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>53291368.35903144</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>1368991084</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>1368991084.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>110.8</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>108.95</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>115.58</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>115.58</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>803674560.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>1096616229.0</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>1096616229</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>944803139.0</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>721693719.98</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>721693719.98</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>22300709.24542224</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>803674560</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>803674560.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>110.2</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>108.92</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>116.09</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>108.92</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>116.09</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>549349456.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>1088283221.6</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>1088283221.6</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>956600754.0</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>713664137.72</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>713664137.72</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>37801512.75292969</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>549349456</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>549349456.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>243.9</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>262.3</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>276.85</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>262.3</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>276.85</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>733798218.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>1194062426.0</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>1194062426</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>1580682611.2</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>1719388067.76</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>1719388067.76</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-66910632.68277311</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>733798218</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>733798218.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>242.6</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>264.23</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>277.41</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>264.23</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>277.41</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>850292929.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>1423462573.4</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>1423462573.4</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>1600931496.7</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>1724439125.3</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>1724439125.3</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-14236824.32551908</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>850292929</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>850292929.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>243.3</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>266.42</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>278.1</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>266.42</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>278.1</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>1357346993.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>1837049872.0</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>1837049872</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>1584059781.4</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>1770696953.38</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>1770696953.38</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>49038355.16075516</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>1357346993</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>1357346993.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>245.8</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>268.5</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>278.92</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>268.5</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>278.92</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>1304530306.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>2208769721.4</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>2208769721.4</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>1552615207.7</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>1804193227.82</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>1804193227.82</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>83352877.74254823</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>1304530306</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>1304530306.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>252.0</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>270.5</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>279.62</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>270.5</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>279.62</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>1724343684.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>2198178141.6</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>2198178141.6</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>1512921772.9</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>1791378007.68</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>1791378007.68</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>135055666.5471616</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>1724343684</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>1724343684.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>256.4</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>272.2</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>280.04</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>272.2</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>280.04</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>1880798955.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>1967302796.4</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>1967302796.4</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>1540485367.4</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>1765544380.32</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>1765544380.32</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>159113371.9627824</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>1880798955</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>1880798955.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>262.7</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>274.62</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>280.55</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>274.62</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>280.55</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>2918229422.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>1778400420.0</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>1778400420</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>1443108304.0</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>1736673951.92</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>1736673951.92</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>171035837.3792841</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>2918229422</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>2918229422.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>268.5</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>276.58</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>280.91</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>276.58</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>280.91</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>3215946240.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>1331069690.8</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>1331069690.8</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>1319551651.8</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>1685350788.7</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>1685350788.7</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>70806243.74645543</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>3215946240</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>3215946240.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>272.5</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>277.7</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>281.06</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>277.7</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>281.06</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>1251572407.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>896460694.0</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>896460694</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>1086040261.5</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>1638145283.6</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>1638145283.6</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>-106805914.934245</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>1251572407</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>1251572407.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>272.6</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>278.32</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>280.98</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>278.32</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>280.98</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>569966958.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>827665404.2</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>827665404.2</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>1063949427.6</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>1639177449.86</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>1639177449.86</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>-146254448.2661656</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>569966958</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>569966958.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>274.3</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>278.77</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>281.12</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>278.77</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>281.12</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>936287073.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>1113667938.4</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>1113667938.4</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>1099219795.8</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>1643378817.02</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>1643378817.02</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-124356967.480832</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>936287073</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>936287073.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>586.6</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>636.0</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>667.3</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>636</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>667.3</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>2251806679.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>2845492684.8</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>2845492684.8</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>3254023064.0</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>2250939639.92</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>2250939639.92</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>80988449.20909452</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>2251806679</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>2251806679.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>577.4</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>640.85</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>668.88</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>640.85</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>668.88</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>2303990317.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>2895931468.2</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>2895931468.2</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>3423927956.4</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>2313304958.2</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>2313304958.2</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>168000892.6023631</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>2303990317</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>2303990317.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>572.0</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>646.8</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>670.44</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>670.4400000000001</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>4282414081.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>3701315712.0</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>3701315712</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>3406103963.5</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>2315429027.54</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>2315429027.54</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>280713247.2140913</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>4282414081</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>4282414081.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>577.0</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>653.25</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>671.96</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>653.25</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>671.96</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>3277325446.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>3639148367.2</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>3639148367.2</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>3149911827.2</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>2279747515.3</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>2279747515.3</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>219731448.8303423</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>3277325446</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>3277325446.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>589.0</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>659.5</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>673.4</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>673.4</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>2111926901.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>3434438489.8</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>3434438489.8</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>3061336173.2</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>2234436035.54</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>2234436035.54</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>232455110.2881894</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>2111926901</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>601.0</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>665.8</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>674.84</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>2504000596.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>3662553443.2</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>3053660242.7</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>2215412102.28</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>367193931.1105347</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>2504000596</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>2504000596.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>617.2</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>672.05</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>676.22</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>672.05</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>676.22</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>6330911536.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>3951924444.6</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>3951924444.6</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>3034497195.4</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>2193079344.64</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>2193079344.64</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>504555995.9956522</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>6330911536</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>6330911536.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>636.8</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>678.2</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>677.46</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>678.2</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>677.46</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>3971577357.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>3110892215.0</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>3110892215</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>2577610128.3</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>2089597881.18</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>2089597881.18</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>272741488.1174035</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>3971577357</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>3971577357.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>647.4</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>681.95</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>677.64</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>681.95</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>677.64</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>2253776059.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>2660675287.2</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>2660675287.2</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>2395309044.8</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>2031062259.28</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>2031062259.28</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>184622942.8942842</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>2253776059</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>2253776059.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>653.6</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>684.55</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>677.36</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>684.55</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>677.36</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>3252501668.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>2688233856.6</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>2688233856.6</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>2353124375.3</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>2012331643.46</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>2012331643.46</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>236195769.4007463</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>3252501668</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>3252501668.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>663.2</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>687.1</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>677.34</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>687.1</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>677.34</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>3950855603.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>2444767042.2</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>2444767042.2</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>2195634921.6</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>1973519631.2</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>1973519631.2</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>194429357.3956661</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>3950855603</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>3950855603.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
